--- a/docs/03_test/社員登録画面テスト.xlsx
+++ b/docs/03_test/社員登録画面テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0177EC06-E3B2-4BE4-A308-3D725F3EAF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD86BBE-6F19-477A-9396-A7C02FAD2D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD2F379E-4E2E-4DC3-A67C-CB666878C08E}"/>
   </bookViews>
@@ -483,78 +483,75 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1401,333 +1398,326 @@
   <cols>
     <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="33.5" customWidth="1"/>
-    <col min="4" max="5" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="49.08203125" customWidth="1"/>
     <col min="7" max="7" width="81.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="14"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="16"/>
+      <c r="B37" s="21"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="2" t="s">
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="12"/>
-      <c r="B39" s="17" t="s">
+      <c r="A39" s="16"/>
+      <c r="B39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="13">
+      <c r="A40" s="5">
         <v>1</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="22">
         <v>36526</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="13">
+      <c r="A41" s="5">
         <v>2</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="22">
         <v>40689</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="13">
+      <c r="A42" s="5">
         <v>3</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="22">
         <v>16582</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="13">
+      <c r="A43" s="5">
         <v>4</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="22">
         <v>36526</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="13">
+      <c r="A44" s="5">
         <v>5</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="22">
         <v>36526</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="13">
+      <c r="A45" s="5">
         <v>6</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="22">
         <v>36526</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="13">
+      <c r="A46" s="5">
         <v>7</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="22">
         <v>36526</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="13">
+      <c r="A47" s="5">
         <v>8</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="22">
         <v>36526</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="15"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="23"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="15"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="23"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="1" t="s">
+      <c r="A48" s="8"/>
+      <c r="B48" s="12"/>
+      <c r="F48" s="8"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="8"/>
+      <c r="B49" s="12"/>
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>36</v>
       </c>
@@ -1769,20 +1759,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="F38:F39"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
